--- a/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
+++ b/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
@@ -385,6 +385,18 @@
       <c r="A2">
         <v>25138</v>
       </c>
+      <c r="B2">
+        <v>517</v>
+      </c>
+      <c r="C2">
+        <v>2.06</v>
+      </c>
+      <c r="D2">
+        <v>24621</v>
+      </c>
+      <c r="E2">
+        <v>97.94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
+++ b/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>24740</v>
+        <v>18133</v>
       </c>
       <c r="B2">
-        <v>384</v>
+        <v>494</v>
       </c>
       <c r="C2">
-        <v>1.55</v>
+        <v>2.72</v>
       </c>
       <c r="D2">
-        <v>24356</v>
+        <v>17639</v>
       </c>
       <c r="E2">
-        <v>98.45</v>
+        <v>97.28</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
+++ b/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>18133</v>
+        <v>23106</v>
       </c>
       <c r="B2">
-        <v>494</v>
+        <v>699</v>
       </c>
       <c r="C2">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="D2">
-        <v>17639</v>
+        <v>22407</v>
       </c>
       <c r="E2">
-        <v>97.28</v>
+        <v>96.97</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
+++ b/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23106</v>
+        <v>23007</v>
       </c>
       <c r="B2">
-        <v>699</v>
+        <v>545</v>
       </c>
       <c r="C2">
-        <v>3.03</v>
+        <v>2.37</v>
       </c>
       <c r="D2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="E2">
-        <v>96.97</v>
+        <v>97.63</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
+++ b/CPRD Raw Analysis/Results/cohort_summary_raw.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23007</v>
+        <v>23106</v>
       </c>
       <c r="B2">
-        <v>545</v>
+        <v>699</v>
       </c>
       <c r="C2">
-        <v>2.37</v>
+        <v>3.03</v>
       </c>
       <c r="D2">
-        <v>22462</v>
+        <v>22407</v>
       </c>
       <c r="E2">
-        <v>97.63</v>
+        <v>96.97</v>
       </c>
     </row>
   </sheetData>
